--- a/Hoadon/HDVao/12/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDVao/12/3502550210_HDDienTuMayTinhTien.xlsx
@@ -2652,12 +2652,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>01/12/2025</t>
+          <t>17/12/2025</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2687,16 +2687,16 @@
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="13" t="n">
-        <v>1.5462963E7</v>
+        <v>6287037.0</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>1237037.0</v>
+        <v>502963.0</v>
       </c>
       <c r="N39" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>1.67E7</v>
+        <v>6790000.0</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -2725,12 +2725,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>930</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>01/12/2025</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -2760,16 +2760,16 @@
       </c>
       <c r="K40" s="6"/>
       <c r="L40" s="13" t="n">
-        <v>2962963.0</v>
+        <v>1.5462963E7</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>237037.0</v>
+        <v>1237037.0</v>
       </c>
       <c r="N40" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O40" s="13" t="n">
-        <v>3200000.0</v>
+        <v>1.67E7</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>C25MDH</t>
+          <t>C25MHN</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>935</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
@@ -2808,17 +2808,17 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>3502399055</t>
+          <t>3502344144</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
+          <t>CÔNG TY TNHH THƯƠNG MẠI VÀ DỊCH VỤ HÙNG NHÂM</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Lô NV 26, đường Bến Chương Dương, khu đô thị Khang Linh, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -2833,16 +2833,16 @@
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="13" t="n">
-        <v>1361574.0</v>
+        <v>2962963.0</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>108926.0</v>
+        <v>237037.0</v>
       </c>
       <c r="N41" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O41" s="13" t="n">
-        <v>1470500.0</v>
+        <v>3200000.0</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -2871,12 +2871,12 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>695</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2906,16 +2906,16 @@
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="13" t="n">
-        <v>1504629.0</v>
+        <v>1361574.0</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>120371.0</v>
+        <v>108926.0</v>
       </c>
       <c r="N42" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O42" s="13" t="n">
-        <v>1625000.0</v>
+        <v>1470500.0</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -2939,32 +2939,32 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MDH</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>727</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>15/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>3502483525</t>
+          <t>3502399055</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
         </is>
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -2974,21 +2974,21 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
       <c r="K43" s="6"/>
       <c r="L43" s="13" t="n">
-        <v>4.2933332E7</v>
+        <v>1504629.0</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>3434667.0</v>
+        <v>120371.0</v>
       </c>
       <c r="N43" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O43" s="13" t="n">
-        <v>4.6367999E7</v>
+        <v>1625000.0</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -3012,32 +3012,32 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>C25MVL</t>
+          <t>C25MDH</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>756</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>3502547722</t>
+          <t>3502399055</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH VĂN LONG MART</t>
+          <t>Công Ty Trách Nhiệm Hữu Hạn Thực Phẩm Đức Hải</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>17/16/6 Hùng Vương, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+          <t>Số 1 Nguyễn Chánh, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam.</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
@@ -3052,23 +3052,169 @@
       </c>
       <c r="K44" s="6"/>
       <c r="L44" s="13" t="n">
-        <v>2314815.0</v>
+        <v>1562500.0</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>185185.0</v>
+        <v>125000.0</v>
       </c>
       <c r="N44" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O44" s="13" t="n">
+        <v>1687500.0</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>15/12/2025</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3502483525</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI ĐẠI Ý 79</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Số 22/18/29 đường Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, TP Hồ Chí Minh , Việt Nam</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH </t>
+        </is>
+      </c>
+      <c r="K45" s="6"/>
+      <c r="L45" s="13" t="n">
+        <v>4.2933332E7</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>3434667.0</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O45" s="13" t="n">
+        <v>4.6367999E7</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C25MVL</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>05/12/2025</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3502547722</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH VĂN LONG MART</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>17/16/6 Hùng Vương, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="K46" s="6"/>
+      <c r="L46" s="13" t="n">
+        <v>2314815.0</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>185185.0</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O46" s="13" t="n">
         <v>2500000.0</v>
       </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
